--- a/E2E_Test_Report_Aivyra.xlsx
+++ b/E2E_Test_Report_Aivyra.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F411"/>
+  <dimension ref="A1:F431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13564,6 +13564,646 @@
         </is>
       </c>
       <c r="F411" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>TC_LOD_001</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Verify login endpoint handles 100 concurrent requests within response time of 500ms</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>TC_LOD_002</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Verify backend database connections pool size scales up under high read loads</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>TC_LOD_003</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Verify landing page loads under simulated 500 concurrent users without timeout</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>TC_LOD_004</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Verify tutor dashboard fetches student analytics database under 200 concurrent student logins</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>TC_LOD_005</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Verify CPU usage remains below 80% on backend server during peak API request spikes</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>TC_LOD_006</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Verify memory leak behavior under sustained high load over 1 hour continuous run</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>TC_LOD_007</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Verify backend API handles sudden traffic spikes of 1000 requests per minute gracefully</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>TC_LOD_008</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Verify audio blob upload handles concurrent file transfers without filesystem lockups</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>TC_LOD_009</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Verify AI models inference route handles 50 concurrent transcription requests</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>TC_LOD_010</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Verify database locks do not occur during simultaneous quiz attempts insertions</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>TC_LOD_011</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Verify Next.js static asset caching handles 1000 concurrent page requests from CDN</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>TC_LOD_012</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Verify rate limiting blocks requests exceeding threshold under distributed brute force</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>TC_LOD_013</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Verify background task queues process email templates under 100 queued items load</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>TC_LOD_014</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Verify SQLite database reads do not block when multiple write queries are queued</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>TC_LOD_015</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Verify frontend bundle size does not cause browser memory crashes under multiple tabs</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>TC_LOD_016</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Verify voice log server cleanup runs in background without impacting main thread CPU</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>TC_LOD_017</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Verify chat messenger route handles concurrent WebSocket connections load</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>TC_LOD_018</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Verify API gateway routes handle cross-origin Preflight requests at scale</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>TC_LOD_019</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Verify database backup operation executes without locking table writes during peak hours</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>TC_LOD_020</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Performance &amp; Load Check</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Verify response time for dashboard courses search queries under 10,000 DB records load</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13580,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13602,7 +14242,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3">
@@ -13668,30 +14308,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Status: Pass</t>
+          <t>Load Testing Tests</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>410</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Status: Fail</t>
+          <t>Status: Pass</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Status: Fail</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Deployment Readiness</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>100% READY</t>
         </is>

--- a/E2E_Test_Report_Aivyra.xlsx
+++ b/E2E_Test_Report_Aivyra.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F431"/>
+  <dimension ref="A1:E431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,11 +440,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
           <t>Status</t>
         </is>
       </c>
@@ -472,11 +467,6 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -504,11 +494,6 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -536,11 +521,6 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -568,11 +548,6 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -600,11 +575,6 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -632,11 +602,6 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -664,11 +629,6 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -696,11 +656,6 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -728,11 +683,6 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -760,11 +710,6 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -792,11 +737,6 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -824,11 +764,6 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -856,11 +791,6 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -888,11 +818,6 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -920,11 +845,6 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -952,11 +872,6 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -984,11 +899,6 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1016,11 +926,6 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1048,11 +953,6 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1080,11 +980,6 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1112,11 +1007,6 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1144,11 +1034,6 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1176,11 +1061,6 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1208,11 +1088,6 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1240,11 +1115,6 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1272,11 +1142,6 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1304,11 +1169,6 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1336,11 +1196,6 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1368,11 +1223,6 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1400,11 +1250,6 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1432,11 +1277,6 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1464,11 +1304,6 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1496,11 +1331,6 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1528,11 +1358,6 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1560,11 +1385,6 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1592,11 +1412,6 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1624,11 +1439,6 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1656,11 +1466,6 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1688,11 +1493,6 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1720,11 +1520,6 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1752,11 +1547,6 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1784,11 +1574,6 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1816,11 +1601,6 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1848,11 +1628,6 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1880,11 +1655,6 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1912,11 +1682,6 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1944,11 +1709,6 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -1976,11 +1736,6 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2008,11 +1763,6 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2040,11 +1790,6 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2072,11 +1817,6 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2104,11 +1844,6 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2136,11 +1871,6 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2168,11 +1898,6 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2200,11 +1925,6 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2232,11 +1952,6 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2264,11 +1979,6 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2296,11 +2006,6 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2328,11 +2033,6 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2360,11 +2060,6 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2392,11 +2087,6 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2424,11 +2114,6 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2456,11 +2141,6 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2488,11 +2168,6 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2520,11 +2195,6 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2552,11 +2222,6 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2584,11 +2249,6 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2616,11 +2276,6 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2648,11 +2303,6 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2680,11 +2330,6 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2712,11 +2357,6 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2744,11 +2384,6 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2776,11 +2411,6 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2808,11 +2438,6 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2840,11 +2465,6 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2872,11 +2492,6 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2904,11 +2519,6 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2936,11 +2546,6 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -2968,11 +2573,6 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3000,11 +2600,6 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3032,11 +2627,6 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3064,11 +2654,6 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3096,11 +2681,6 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3128,11 +2708,6 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3160,11 +2735,6 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3192,11 +2762,6 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3224,11 +2789,6 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3256,11 +2816,6 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3288,11 +2843,6 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3320,11 +2870,6 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3352,11 +2897,6 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3384,11 +2924,6 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3416,11 +2951,6 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3448,11 +2978,6 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3480,11 +3005,6 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3512,11 +3032,6 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3544,11 +3059,6 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3576,11 +3086,6 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3608,11 +3113,6 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3640,11 +3140,6 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3672,11 +3167,6 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3704,11 +3194,6 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3736,11 +3221,6 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3768,11 +3248,6 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3800,11 +3275,6 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3832,11 +3302,6 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3864,11 +3329,6 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3896,11 +3356,6 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3928,11 +3383,6 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3960,11 +3410,6 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -3992,11 +3437,6 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4024,11 +3464,6 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4056,11 +3491,6 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4088,11 +3518,6 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4120,11 +3545,6 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4152,11 +3572,6 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4184,11 +3599,6 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4216,11 +3626,6 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4248,11 +3653,6 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4280,11 +3680,6 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4312,11 +3707,6 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4344,11 +3734,6 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4376,11 +3761,6 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4408,11 +3788,6 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4440,11 +3815,6 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4472,11 +3842,6 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4504,11 +3869,6 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4536,11 +3896,6 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4568,11 +3923,6 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4600,11 +3950,6 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4632,11 +3977,6 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4664,11 +4004,6 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4696,11 +4031,6 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4728,11 +4058,6 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4760,11 +4085,6 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4792,11 +4112,6 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4824,11 +4139,6 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4856,11 +4166,6 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4888,11 +4193,6 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4920,11 +4220,6 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4952,11 +4247,6 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -4984,11 +4274,6 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5016,11 +4301,6 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5048,11 +4328,6 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5080,11 +4355,6 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5112,11 +4382,6 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5144,11 +4409,6 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5176,11 +4436,6 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5208,11 +4463,6 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5240,11 +4490,6 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5272,11 +4517,6 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5304,11 +4544,6 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5336,11 +4571,6 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5368,11 +4598,6 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5400,11 +4625,6 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5432,11 +4652,6 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5464,11 +4679,6 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5496,11 +4706,6 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5528,11 +4733,6 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5560,11 +4760,6 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5592,11 +4787,6 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5624,11 +4814,6 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5656,11 +4841,6 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5688,11 +4868,6 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5720,11 +4895,6 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5752,11 +4922,6 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5784,11 +4949,6 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5816,11 +4976,6 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5848,11 +5003,6 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5880,11 +5030,6 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5912,11 +5057,6 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5944,11 +5084,6 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -5976,11 +5111,6 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6008,11 +5138,6 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6040,11 +5165,6 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6072,11 +5192,6 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6104,11 +5219,6 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6136,11 +5246,6 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6168,11 +5273,6 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6200,11 +5300,6 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6232,11 +5327,6 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6264,11 +5354,6 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6296,11 +5381,6 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6328,11 +5408,6 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6360,11 +5435,6 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6392,11 +5462,6 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6424,11 +5489,6 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6456,11 +5516,6 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6488,11 +5543,6 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6520,11 +5570,6 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6552,11 +5597,6 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6584,11 +5624,6 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6616,11 +5651,6 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6648,11 +5678,6 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6680,11 +5705,6 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6712,11 +5732,6 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6744,11 +5759,6 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6776,11 +5786,6 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6808,11 +5813,6 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6840,11 +5840,6 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6872,11 +5867,6 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6904,11 +5894,6 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6936,11 +5921,6 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -6968,11 +5948,6 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7000,11 +5975,6 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7032,11 +6002,6 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7064,11 +6029,6 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7096,11 +6056,6 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7128,11 +6083,6 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7160,11 +6110,6 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7192,11 +6137,6 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7224,11 +6164,6 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7256,11 +6191,6 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7288,11 +6218,6 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7320,11 +6245,6 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7352,11 +6272,6 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7384,11 +6299,6 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7416,11 +6326,6 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7448,11 +6353,6 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7480,11 +6380,6 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7512,11 +6407,6 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7544,11 +6434,6 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7576,11 +6461,6 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7608,11 +6488,6 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7640,11 +6515,6 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7672,11 +6542,6 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7704,11 +6569,6 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7736,11 +6596,6 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7768,11 +6623,6 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7800,11 +6650,6 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7832,11 +6677,6 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7864,11 +6704,6 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7896,11 +6731,6 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7928,11 +6758,6 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7960,11 +6785,6 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -7992,11 +6812,6 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8024,11 +6839,6 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8056,11 +6866,6 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8088,11 +6893,6 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8120,11 +6920,6 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8152,11 +6947,6 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8184,11 +6974,6 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8216,11 +7001,6 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8248,11 +7028,6 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8280,11 +7055,6 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8312,11 +7082,6 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8344,11 +7109,6 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8376,11 +7136,6 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8408,11 +7163,6 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8440,11 +7190,6 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8472,11 +7217,6 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8504,11 +7244,6 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8536,11 +7271,6 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8568,11 +7298,6 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8600,11 +7325,6 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8632,11 +7352,6 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8664,11 +7379,6 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8696,11 +7406,6 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8728,11 +7433,6 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8760,11 +7460,6 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8792,11 +7487,6 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8824,11 +7514,6 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8856,11 +7541,6 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8888,11 +7568,6 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8920,11 +7595,6 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8952,11 +7622,6 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -8984,11 +7649,6 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9016,11 +7676,6 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9048,11 +7703,6 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9080,11 +7730,6 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9112,11 +7757,6 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9144,11 +7784,6 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9176,11 +7811,6 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9208,11 +7838,6 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9240,11 +7865,6 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9272,11 +7892,6 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9304,11 +7919,6 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9336,11 +7946,6 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9368,11 +7973,6 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9400,11 +8000,6 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F281" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9432,11 +8027,6 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9464,11 +8054,6 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9496,11 +8081,6 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9528,11 +8108,6 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9560,11 +8135,6 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9592,11 +8162,6 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9624,11 +8189,6 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9656,11 +8216,6 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9688,11 +8243,6 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9720,11 +8270,6 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9752,11 +8297,6 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9784,11 +8324,6 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9816,11 +8351,6 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9848,11 +8378,6 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9880,11 +8405,6 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9912,11 +8432,6 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9944,11 +8459,6 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -9976,11 +8486,6 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10008,11 +8513,6 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10040,11 +8540,6 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10072,11 +8567,6 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10104,11 +8594,6 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10136,11 +8621,6 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10168,11 +8648,6 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10200,11 +8675,6 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10232,11 +8702,6 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10264,11 +8729,6 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10296,11 +8756,6 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10328,11 +8783,6 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10360,11 +8810,6 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10392,11 +8837,6 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10424,11 +8864,6 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10456,11 +8891,6 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10488,11 +8918,6 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10520,11 +8945,6 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10552,11 +8972,6 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10584,11 +8999,6 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10616,11 +9026,6 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10648,11 +9053,6 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10680,11 +9080,6 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10712,11 +9107,6 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10744,11 +9134,6 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10776,11 +9161,6 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10808,11 +9188,6 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10840,11 +9215,6 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10872,11 +9242,6 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10904,11 +9269,6 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F328" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10936,11 +9296,6 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -10968,11 +9323,6 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11000,11 +9350,6 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11032,11 +9377,6 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11064,11 +9404,6 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11096,11 +9431,6 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11128,11 +9458,6 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11160,11 +9485,6 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F336" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11192,11 +9512,6 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11224,11 +9539,6 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11256,11 +9566,6 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11288,11 +9593,6 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11320,11 +9620,6 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11352,11 +9647,6 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11384,11 +9674,6 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11416,11 +9701,6 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11448,11 +9728,6 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11480,11 +9755,6 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11512,11 +9782,6 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11544,11 +9809,6 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11576,11 +9836,6 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11608,11 +9863,6 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11640,11 +9890,6 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F351" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11672,11 +9917,6 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11704,11 +9944,6 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11736,11 +9971,6 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11768,11 +9998,6 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11800,11 +10025,6 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11832,11 +10052,6 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11864,11 +10079,6 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11896,11 +10106,6 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11928,11 +10133,6 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11960,11 +10160,6 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -11992,11 +10187,6 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12024,11 +10214,6 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12056,11 +10241,6 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12088,11 +10268,6 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12120,11 +10295,6 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12152,11 +10322,6 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12184,11 +10349,6 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F368" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12216,11 +10376,6 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12248,11 +10403,6 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12280,11 +10430,6 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12312,11 +10457,6 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12344,11 +10484,6 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12376,11 +10511,6 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12408,11 +10538,6 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12440,11 +10565,6 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12472,11 +10592,6 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12504,11 +10619,6 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12536,11 +10646,6 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12568,11 +10673,6 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12600,11 +10700,6 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12632,11 +10727,6 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12664,11 +10754,6 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12696,11 +10781,6 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12728,11 +10808,6 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12760,11 +10835,6 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12792,11 +10862,6 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12824,11 +10889,6 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12856,11 +10916,6 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12888,11 +10943,6 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12920,11 +10970,6 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12952,11 +10997,6 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -12984,11 +11024,6 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13016,11 +11051,6 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13048,11 +11078,6 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13080,11 +11105,6 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13112,11 +11132,6 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13144,11 +11159,6 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13176,11 +11186,6 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13208,11 +11213,6 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13240,11 +11240,6 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13272,11 +11267,6 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13304,11 +11294,6 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13336,11 +11321,6 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13368,11 +11348,6 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13400,11 +11375,6 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13432,11 +11402,6 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13464,11 +11429,6 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13496,11 +11456,6 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13528,11 +11483,6 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13560,11 +11510,6 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13592,11 +11537,6 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13624,11 +11564,6 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13656,11 +11591,6 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13688,11 +11618,6 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13720,11 +11645,6 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13752,11 +11672,6 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13784,11 +11699,6 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13816,11 +11726,6 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13848,11 +11753,6 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13880,11 +11780,6 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13912,11 +11807,6 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13944,11 +11834,6 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -13976,11 +11861,6 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14008,11 +11888,6 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14040,11 +11915,6 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14072,11 +11942,6 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14104,11 +11969,6 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14136,11 +11996,6 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14168,11 +12023,6 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
           <t>Pass</t>
         </is>
       </c>
@@ -14199,11 +12049,6 @@
         </is>
       </c>
       <c r="E431" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
